--- a/mariano-os/areas/ministerio/recursos/Ruge_reparto_tareas_17ago2026_actualizado.xlsx
+++ b/mariano-os/areas/ministerio/recursos/Ruge_reparto_tareas_17ago2026_actualizado.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="14">
     <font>
       <name val="Calibri"/>
@@ -187,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -249,6 +251,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,7 +678,11 @@
           <t>26 ago</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Ver detalle por ítem (repartido)</t>
+        </is>
+      </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Ver miercoles 19 ago (pendiente respuesta de Mauricio sobre lote de piscina)</t>
@@ -686,7 +695,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>PENDIENTE 17 ago: parte de esto (arena, cajas de requisa, cuerdas de piscina) podria ser del equipo de Eventos (Mauricio y Cristian, lo gestionaron el reto pasado) - Julio le pregunta a Mauricio quien lo compro y donde antes de asignar encargado final. | ACTUALIZADO 17 ago (2da revision, tras subir el inventario real): se sumaron 26 items mas que figuraban como ALMACEN RUGE en el inventario original y se habian quedado afuera del detalle. Ninguno se discutio en la llamada, siguen sin encargado.</t>
+          <t>PENDIENTE 17 ago: parte de esto (arena, cajas de requisa, cuerdas de piscina) podria ser del equipo de Eventos (Mauricio y Cristian, lo gestionaron el reto pasado) - Julio le pregunta a Mauricio quien lo compro y donde antes de asignar encargado final. | ACTUALIZADO 17 ago (2da revision, tras subir el inventario real): se sumaron 26 items mas que figuraban como ALMACEN RUGE en el inventario original y se habian quedado afuera del detalle. Ninguno se discutio en la llamada, siguen sin encargado. | REPARTO FINAL 17 ago (version de Mariano, ver ruge_reparto_lookup.md): Repartido: David Luzuriaga (29 items), Marco Guanuchi (4 items) - version final de Mariano 17 ago.</t>
         </is>
       </c>
     </row>
@@ -851,7 +860,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Marco Guanuchi</t>
+          <t>Ver detalle por ítem (repartido)</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -866,7 +875,7 @@
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>Pedir a Nestor si puede prestar nuevamente las cuerdas, Pedir estuche insulina a Marco,  mantel verde, las mesas ya están en Xodos, Pedir radios (y ver si funcionan todas a Administración de la iglesia), altavoz pedir a Chiriguaya | ACTUALIZADO 17 ago (llamada reparto): Altavoz: pedir a Chiriguaya. Cuerdas: pedirle a Nestor si las vuelve a prestar (las presto el la vez pasada). Estuche de insulina: lo tiene Marco Guanuchi. Mantel verde: comprar. Mesas: ya estan en Xodos, confirmar. Radios de iglesia x10: hablar con Juliana (administracion) y verificar que funcionen todas.</t>
+          <t>Pedir a Nestor si puede prestar nuevamente las cuerdas, Pedir estuche insulina a Marco,  mantel verde, las mesas ya están en Xodos, Pedir radios (y ver si funcionan todas a Administración de la iglesia), altavoz pedir a Chiriguaya | ACTUALIZADO 17 ago (llamada reparto): Altavoz: pedir a Chiriguaya. Cuerdas: pedirle a Nestor si las vuelve a prestar (las presto el la vez pasada). Estuche de insulina: lo tiene Marco Guanuchi. Mantel verde: comprar. Mesas: ya estan en Xodos, confirmar. Radios de iglesia x10: hablar con Juliana (administracion) y verificar que funcionen todas. | REPARTO FINAL 17 ago (version de Mariano, ver ruge_reparto_lookup.md): Mayoría Marco Guanuchi, 1 ítem (alargador eléctrico) con Julio Cesar Navia.</t>
         </is>
       </c>
     </row>
@@ -896,7 +905,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Julio Cesar Navia</t>
+          <t>Ver detalle por ítem (repartido)</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -911,7 +920,7 @@
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Julio se hace cargo de hablar con Mateo y Jefferson por camion cerrado y furgoneta, Marco del bus y lo ve con Guanuchi, David de la pick up, Marco de radios y telefonos satalitales. Julio se encarga del conjunto de tareas | ACTUALIZADO 17 ago (llamada reparto): Bus 55 plazas: Marco Guanuchi habla con Andres Uquillas (quien lo alquilo la vez pasada) por el mismo presupuesto para la nueva fecha, Julio le hace seguimiento. Camion cerrado y furgoneta: Julio habla con Mateo y Jefferson. Radios VHF x15 y telefonos satelitales x2: Marco Guanuchi busca la empresa de alquiler. Troncos: Julio contacta al mismo vendedor con el que nego Marco Jurado el ano pasado, para el 2-3 de octubre. Pick-up / camion caja abierta: David busca donde alquilarla. Julio es el encargado del conjunto y le reporta a Mariano.</t>
+          <t>Julio se hace cargo de hablar con Mateo y Jefferson por camion cerrado y furgoneta, Marco del bus y lo ve con Guanuchi, David de la pick up, Marco de radios y telefonos satalitales. Julio se encarga del conjunto de tareas | ACTUALIZADO 17 ago (llamada reparto): Bus 55 plazas: Marco Guanuchi habla con Andres Uquillas (quien lo alquilo la vez pasada) por el mismo presupuesto para la nueva fecha, Julio le hace seguimiento. Camion cerrado y furgoneta: Julio habla con Mateo y Jefferson. Radios VHF x15 y telefonos satelitales x2: Marco Guanuchi busca la empresa de alquiler. Troncos: Julio contacta al mismo vendedor con el que nego Marco Jurado el ano pasado, para el 2-3 de octubre. Pick-up / camion caja abierta: David busca donde alquilarla. Julio es el encargado del conjunto y le reporta a Mariano. | REPARTO FINAL 17 ago (version de Mariano, ver ruge_reparto_lookup.md): Repartido: Marco Guanuchi (bus, radios VHF, satelital), Julio Cesar Navia (camión cerrado, furgoneta, troncos), David Luzuriaga (camión caja abierta).</t>
         </is>
       </c>
     </row>
@@ -941,7 +950,7 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Julio Cesar Navia</t>
+          <t>Ver detalle por ítem (repartido)</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -956,7 +965,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Julio habla con Mauricio para saber quién compró todo y pide presupuestos, ,Marco se encarga de figuras de premios hablar con Richard, Fuegos pirotecnicos hablar con el pastor, guantes normales, paja donde se compra la arena, tierra es lo mismo. | ACTUALIZADO 17 ago (llamada reparto): Bolsas de basura y ziploc: Mercadona. Fuegos pirotecnicos y guantes normales: cualquier sitio (guantes ya acordados con Marco Jurado). Cinta reflectante y figuras de premios: van con el contacto de Marco Jurado / su sobrino Richard, dentro del bloque de Julio (Mariano NO gestiona esto directo — el solo recibe el presupuesto final para pasarlo a administracion, como coordinador general, no como ejecutor de tareas de campo). Arena y paja son del lote de piscina - Julio le pregunta a Mauricio (Eventos) quien lo compro y donde el reto pasado, pendiente su respuesta antes de asignar encargado final de esa parte.</t>
+          <t>Julio habla con Mauricio para saber quién compró todo y pide presupuestos, ,Marco se encarga de figuras de premios hablar con Richard, Fuegos pirotecnicos hablar con el pastor, guantes normales, paja donde se compra la arena, tierra es lo mismo. | ACTUALIZADO 17 ago (llamada reparto): Bolsas de basura y ziploc: Mercadona. Fuegos pirotecnicos y guantes normales: cualquier sitio (guantes ya acordados con Marco Jurado). Cinta reflectante y figuras de premios: van con el contacto de Marco Jurado / su sobrino Richard, dentro del bloque de Julio (Mariano NO gestiona esto directo — el solo recibe el presupuesto final para pasarlo a administracion, como coordinador general, no como ejecutor de tareas de campo). Arena y paja son del lote de piscina - Julio le pregunta a Mauricio (Eventos) quien lo compro y donde el reto pasado, pendiente su respuesta antes de asignar encargado final de esa parte. | REPARTO FINAL 17 ago (version de Mariano, ver ruge_reparto_lookup.md): Repartido: Marco Guanuchi (9), Julio Cesar Navia (7), David Luzuriaga (7) - version final de Mariano 17 ago.</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2614,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Iglesia Impact Valencia</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -2641,7 +2650,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Prestado por Marcos J.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Prestado por Marcos J.</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -2678,8 +2687,16 @@
         <v>30</v>
       </c>
       <c r="F7" s="9" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2704,8 +2721,16 @@
         <v>90</v>
       </c>
       <c r="F8" s="9" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2730,8 +2755,16 @@
         <v>5</v>
       </c>
       <c r="F9" s="9" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2756,8 +2789,16 @@
         <v>5</v>
       </c>
       <c r="F10" s="9" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2781,9 +2822,19 @@
       <c r="E11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2805,9 +2856,19 @@
       <c r="E12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -2832,8 +2893,16 @@
         <v>200</v>
       </c>
       <c r="F13" s="9" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2857,7 +2926,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Metal o madera desmontable — valorar que la haga Néstor</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Metal o madera desmontable — valorar que la haga Néstor</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -2893,7 +2962,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Mandarlo hacer — Levis</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Mandarlo hacer — Levis</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -2929,7 +2998,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Mandarlo hacer — Levis</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Mandarlo hacer — Levis</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -2965,7 +3034,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Mandarlo hacer — Marcos Chiriguaya</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Mandarlo hacer — Marcos Chiriguaya</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -3065,7 +3134,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Necesita tiempo de envío desde Costa Rica</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -3101,7 +3170,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Sumar talla doble de grande (corrección retrospectiva)</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -3135,7 +3204,11 @@
       <c r="E22" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="F22" s="9" t="n"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
+        </is>
+      </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Marco Guanuchi</t>
@@ -3169,7 +3242,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Por comisión</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -3205,7 +3278,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Sumar talla doble de grande (corrección retrospectiva)</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -3239,7 +3312,11 @@
       <c r="E25" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="F25" s="9" t="n"/>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
+        </is>
+      </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Marco Guanuchi</t>
@@ -3273,7 +3350,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Marcos Chiriguaya y Mariano B.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Marcos Chiriguaya y Mariano B.</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -3309,7 +3386,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Néstor</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Néstor</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3347,7 +3424,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Marco Guanuchi</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Marco Guanuchi</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -3374,7 +3451,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>MANTEL NEGRO PARA MESA DE CAMISETAS</t>
+          <t>MANTEL VERDE PARA MESA DE CAMISETAS</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -3383,7 +3460,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Iglesia Impact Valencia</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -3419,7 +3496,7 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Local multiusos Xodos</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Local multiusos Xodos</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -3455,7 +3532,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Iglesia Impact Valencia</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3491,7 +3568,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Algún servidor</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Buscar alquiler y pasar presupuesto a Administración (Juliana) </t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -3527,12 +3604,12 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Iglesia Impact Valencia</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Administración (Juliana) </t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Marco Guanuchi</t>
+          <t>Julio Cesar Navia</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -3563,7 +3640,7 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>MÁXIMA URGENCIA — reservar con tiempo</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Buscar alquiler y pasar presupuesto a Administración (Juliana) </t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3599,7 +3676,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>MÁXIMA URGENCIA</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): MÁXIMA URGENCIA</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -3635,7 +3712,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Valorar opciones con Mateo y Jefferson</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Valorar opciones con Mateo y Jefferson</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3671,7 +3748,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Valorar opción con Jefferson</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Valorar opción con Jefferson</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3707,7 +3784,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>MÁXIMA URGENCIA</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Buscar alquiler y pasar presupuesto a Administración (Juliana) </t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3743,7 +3820,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>MÁXIMA URGENCIA</t>
+          <t xml:space="preserve">CONFIRMADO 17 ago (version final Mariano): Buscar alquiler y pasar presupuesto a Administración (Juliana) </t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -3779,7 +3856,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Hombre del pueblo</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Hombre del pueblo</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -3815,9 +3892,19 @@
           <t>30 sacos</t>
         </is>
       </c>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA  Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="19">
       <c r="A42" s="7" t="inlineStr">
@@ -3969,7 +4056,7 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Valorar opción con Richard</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Valorar opción con Richard</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4067,9 +4154,19 @@
       <c r="E49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA  Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="19">
       <c r="A50" s="7" t="inlineStr">
@@ -4091,9 +4188,19 @@
       <c r="E50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="19">
       <c r="A51" s="7" t="inlineStr">
@@ -4115,9 +4222,19 @@
       <c r="E51" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="19">
       <c r="A52" s="7" t="inlineStr">
@@ -4139,9 +4256,19 @@
       <c r="E52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" s="7" t="inlineStr">
@@ -4163,9 +4290,19 @@
       <c r="E53" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="F53" s="9" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA  Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="19">
       <c r="A54" s="7" t="inlineStr">
@@ -4190,8 +4327,16 @@
         <v>100</v>
       </c>
       <c r="F54" s="9" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="19">
       <c r="A55" s="7" t="inlineStr">
@@ -4218,8 +4363,16 @@
         <v>200</v>
       </c>
       <c r="F55" s="9" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="19">
       <c r="A56" s="7" t="inlineStr">
@@ -4241,9 +4394,19 @@
       <c r="E56" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="19">
       <c r="A57" s="7" t="inlineStr">
@@ -4270,8 +4433,16 @@
         <v>4</v>
       </c>
       <c r="F57" s="9" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="19">
       <c r="A58" s="7" t="inlineStr">
@@ -4298,8 +4469,16 @@
         <v>100</v>
       </c>
       <c r="F58" s="9" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="19">
       <c r="A59" s="7" t="inlineStr">
@@ -4322,8 +4501,16 @@
         <v>100</v>
       </c>
       <c r="F59" s="9" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="19">
       <c r="A60" s="7" t="inlineStr">
@@ -4346,8 +4533,16 @@
         <v>100</v>
       </c>
       <c r="F60" s="9" t="n"/>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="19">
       <c r="A61" s="7" t="inlineStr">
@@ -4370,8 +4565,16 @@
         <v>100</v>
       </c>
       <c r="F61" s="9" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="19">
       <c r="A62" s="7" t="inlineStr">
@@ -4396,8 +4599,16 @@
         <v>100</v>
       </c>
       <c r="F62" s="9" t="n"/>
-      <c r="G62" s="10" t="n"/>
-      <c r="H62" s="10" t="n"/>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="19">
       <c r="A63" s="7" t="inlineStr">
@@ -4424,8 +4635,16 @@
         <v>100</v>
       </c>
       <c r="F63" s="9" t="n"/>
-      <c r="G63" s="10" t="n"/>
-      <c r="H63" s="10" t="n"/>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>Marco Guanuchi</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>9 sept</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="19">
       <c r="A64" s="13" t="inlineStr">
@@ -4485,7 +4704,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>⚠ Retro decía faltan 2 — confirmar cuál dato es correcto</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ⚠ Retro decía faltan 2 — confirmar cuál dato es correcto</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -4593,7 +4812,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Colgar lona piedra Xodos</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Colgar lona piedra Xodos</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -4631,7 +4850,7 @@
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>Cartel bienvenida</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Cartel bienvenida</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -4829,7 +5048,7 @@
       <c r="E75" s="9" t="n"/>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Construcción a cargo de Marcos Chiriguaya, confirmar que lo tiene listo</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Construcción a cargo de Marcos Chiriguaya, confirmar que lo tiene listo</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -4867,7 +5086,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Ya completo — solo confirmar que están en almacén</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Ya completo — solo confirmar que están en almacén</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -5671,7 +5890,7 @@
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>Marcos Chiriguaya</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Marcos Chiriguaya</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -5707,7 +5926,7 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>1 Marcos J. + buscar otro</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): 1 Marcos J. + buscar otro</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -5743,7 +5962,7 @@
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>Marcos Jurado</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Marcos Jurado</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -5779,7 +5998,7 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Marcos Chiriguaya</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Marcos Chiriguaya</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -5815,7 +6034,7 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>Iglesia Impact Valencia</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): Iglesia Impact Valencia</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -6037,7 +6256,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6290,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6324,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6358,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6392,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6426,7 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6460,7 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6494,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6528,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6564,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6598,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6634,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6668,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6704,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6740,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6774,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6810,7 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6846,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6882,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6918,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6954,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6990,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6807,7 +7026,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6841,7 +7060,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7094,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6909,7 +7128,7 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6943,7 +7162,7 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -6979,7 +7198,7 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7234,7 @@
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7270,7 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7304,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7340,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7374,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7191,7 +7410,7 @@
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7446,7 @@
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7482,7 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7518,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7552,7 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7586,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7620,7 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7656,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7692,7 @@
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7724,7 @@
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7760,7 @@
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7796,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7832,7 @@
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7868,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7902,7 @@
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7936,7 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7970,7 @@
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7785,7 +8004,7 @@
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7821,7 +8040,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7857,7 +8076,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7893,7 +8112,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7929,7 +8148,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -7965,7 +8184,7 @@
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8220,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8254,7 @@
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8288,7 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>28 sept</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8350,7 @@
       <c r="E171" s="9" t="n"/>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>O coordinar hacerlo días antes; David puede prestar herramienta de obra</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): O coordinar hacerlo días antes; David puede prestar herramienta de obra</t>
         </is>
       </c>
       <c r="G171" s="10" t="inlineStr">
@@ -8141,7 +8360,7 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8390,7 @@
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8420,7 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26 ago</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8444,7 @@
       <c r="E174" s="9" t="n"/>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G174" s="10" t="inlineStr">
@@ -8259,7 +8478,7 @@
       <c r="E175" s="9" t="n"/>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G175" s="10" t="inlineStr">
@@ -8293,7 +8512,7 @@
       <c r="E176" s="9" t="n"/>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G176" s="10" t="inlineStr">
@@ -8327,7 +8546,7 @@
       <c r="E177" s="9" t="n"/>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G177" s="10" t="inlineStr">
@@ -8361,7 +8580,7 @@
       <c r="E178" s="9" t="n"/>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G178" s="10" t="inlineStr">
@@ -8395,7 +8614,7 @@
       <c r="E179" s="9" t="n"/>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G179" s="10" t="inlineStr">
@@ -8429,7 +8648,7 @@
       <c r="E180" s="9" t="n"/>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
+          <t>CONFIRMADO 17 ago (version final Mariano): ALMACEN RUGE (ya en stock) — confirmar con Adrián Rivera que esté en buen estado y la cantidad correcta.</t>
         </is>
       </c>
       <c r="G180" s="10" t="inlineStr">
@@ -8463,11 +8682,17 @@
       <c r="E181" s="9" t="n"/>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G181" s="10" t="n"/>
-      <c r="H181" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G181" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H181" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="19">
       <c r="A182" s="7" t="inlineStr">
@@ -8489,11 +8714,17 @@
       <c r="E182" s="9" t="n"/>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G182" s="10" t="n"/>
-      <c r="H182" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G182" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H182" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="19">
       <c r="A183" s="7" t="inlineStr">
@@ -8515,11 +8746,17 @@
       <c r="E183" s="9" t="n"/>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G183" s="10" t="n"/>
-      <c r="H183" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G183" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H183" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="19">
       <c r="A184" s="7" t="inlineStr">
@@ -8541,11 +8778,17 @@
       <c r="E184" s="9" t="n"/>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G184" s="10" t="n"/>
-      <c r="H184" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G184" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H184" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="185" ht="15.75" customHeight="1" s="19">
       <c r="A185" s="7" t="inlineStr">
@@ -8567,11 +8810,17 @@
       <c r="E185" s="9" t="n"/>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G185" s="10" t="n"/>
-      <c r="H185" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G185" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H185" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="186" ht="15.75" customHeight="1" s="19">
       <c r="A186" s="7" t="inlineStr">
@@ -8593,11 +8842,17 @@
       <c r="E186" s="9" t="n"/>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G186" s="10" t="n"/>
-      <c r="H186" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y GUIAS</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H186" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="19">
       <c r="A187" s="7" t="inlineStr">
@@ -8619,11 +8874,17 @@
       <c r="E187" s="9" t="n"/>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G187" s="10" t="n"/>
-      <c r="H187" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G187" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H187" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="188" ht="15.75" customHeight="1" s="19">
       <c r="A188" s="7" t="inlineStr">
@@ -8645,11 +8906,17 @@
       <c r="E188" s="9" t="n"/>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G188" s="10" t="n"/>
-      <c r="H188" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G188" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H188" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="19">
       <c r="A189" s="7" t="inlineStr">
@@ -8671,11 +8938,17 @@
       <c r="E189" s="9" t="n"/>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G189" s="10" t="n"/>
-      <c r="H189" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G189" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H189" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="190" ht="15.75" customHeight="1" s="19">
       <c r="A190" s="7" t="inlineStr">
@@ -8697,11 +8970,17 @@
       <c r="E190" s="9" t="n"/>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G190" s="10" t="n"/>
-      <c r="H190" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y GUIAS</t>
+        </is>
+      </c>
+      <c r="G190" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H190" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="19">
       <c r="A191" s="7" t="inlineStr">
@@ -8723,11 +9002,17 @@
       <c r="E191" s="9" t="n"/>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G191" s="10" t="n"/>
-      <c r="H191" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G191" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H191" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="19">
       <c r="A192" s="7" t="inlineStr">
@@ -8749,11 +9034,17 @@
       <c r="E192" s="9" t="n"/>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G192" s="10" t="n"/>
-      <c r="H192" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H192" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="19">
       <c r="A193" s="7" t="inlineStr">
@@ -8775,11 +9066,17 @@
       <c r="E193" s="9" t="n"/>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G193" s="10" t="n"/>
-      <c r="H193" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G193" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H193" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="19">
       <c r="A194" s="7" t="inlineStr">
@@ -8801,11 +9098,17 @@
       <c r="E194" s="9" t="n"/>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G194" s="10" t="n"/>
-      <c r="H194" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H194" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="19">
       <c r="A195" s="7" t="inlineStr">
@@ -8827,11 +9130,17 @@
       <c r="E195" s="9" t="n"/>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G195" s="10" t="n"/>
-      <c r="H195" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G195" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H195" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="19">
       <c r="A196" s="7" t="inlineStr">
@@ -8853,11 +9162,17 @@
       <c r="E196" s="9" t="n"/>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G196" s="10" t="n"/>
-      <c r="H196" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G196" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H196" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="19">
       <c r="A197" s="7" t="inlineStr">
@@ -8879,11 +9194,17 @@
       <c r="E197" s="9" t="n"/>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G197" s="10" t="n"/>
-      <c r="H197" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G197" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H197" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="19">
       <c r="A198" s="7" t="inlineStr">
@@ -8905,11 +9226,17 @@
       <c r="E198" s="9" t="n"/>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G198" s="10" t="n"/>
-      <c r="H198" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H198" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="19">
       <c r="A199" s="7" t="inlineStr">
@@ -8931,11 +9258,17 @@
       <c r="E199" s="9" t="n"/>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G199" s="10" t="n"/>
-      <c r="H199" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G199" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H199" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="19">
       <c r="A200" s="7" t="inlineStr">
@@ -8957,11 +9290,17 @@
       <c r="E200" s="9" t="n"/>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G200" s="10" t="n"/>
-      <c r="H200" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H200" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="19">
       <c r="A201" s="7" t="inlineStr">
@@ -8983,11 +9322,17 @@
       <c r="E201" s="9" t="n"/>
       <c r="F201" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G201" s="10" t="n"/>
-      <c r="H201" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="G201" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H201" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="19">
       <c r="A202" s="7" t="inlineStr">
@@ -9009,11 +9354,17 @@
       <c r="E202" s="9" t="n"/>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G202" s="10" t="n"/>
-      <c r="H202" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G202" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H202" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="19">
       <c r="A203" s="7" t="inlineStr">
@@ -9035,11 +9386,17 @@
       <c r="E203" s="9" t="n"/>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G203" s="10" t="n"/>
-      <c r="H203" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G203" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H203" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="19">
       <c r="A204" s="7" t="inlineStr">
@@ -9061,11 +9418,17 @@
       <c r="E204" s="9" t="n"/>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G204" s="10" t="n"/>
-      <c r="H204" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y GUIAS</t>
+        </is>
+      </c>
+      <c r="G204" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H204" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="19">
       <c r="A205" s="7" t="inlineStr">
@@ -9087,11 +9450,17 @@
       <c r="E205" s="9" t="n"/>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G205" s="10" t="n"/>
-      <c r="H205" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G205" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H205" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="19">
       <c r="A206" s="7" t="inlineStr">
@@ -9113,11 +9482,17 @@
       <c r="E206" s="9" t="n"/>
       <c r="F206" s="9" t="inlineStr">
         <is>
-          <t>ALMACEN RUGE (ya en stock) — no se discutió en la llamada del 17 ago, pendiente asignar encargado y verificar en la reunión del miércoles. Agregado 17 ago al detectar que faltaba en el detalle original.</t>
-        </is>
-      </c>
-      <c r="G206" s="10" t="n"/>
-      <c r="H206" s="10" t="n"/>
+          <t>CONFIRMADO 17 ago (version final Mariano): LOGÍSTICA Y EVENTOS</t>
+        </is>
+      </c>
+      <c r="G206" s="10" t="inlineStr">
+        <is>
+          <t>David Luzuriaga</t>
+        </is>
+      </c>
+      <c r="H206" s="27" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="19"/>
     <row r="208" ht="15.75" customHeight="1" s="19"/>
